--- a/Testing/Security-Audit/Vulnerability Test Results/findings.xlsx
+++ b/Testing/Security-Audit/Vulnerability Test Results/findings.xlsx
@@ -397,301 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Finding ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Severity</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Vulnerability Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>CWE Mapping</v>
-      </c>
-      <c r="E1" t="str">
-        <v>OWASP Mapping</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Endpoint</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Impact</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Remediation</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>VULN_001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Authorization &amp; RBAC</v>
-      </c>
-      <c r="D2" t="str">
-        <v>CWE-243</v>
-      </c>
-      <c r="E2" t="str">
-        <v>A08:2021</v>
-      </c>
-      <c r="F2" t="str">
-        <v>/api/v1/auth/register</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #13</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>VULN_002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>HIGH</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Input Validation &amp; Sanitization</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CWE-236</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A06:2021</v>
-      </c>
-      <c r="F3" t="str">
-        <v>/api/v1/products</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #16</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>VULN_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Injection (SQL, NoSQL, Command)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>CWE-229</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A04:2021</v>
-      </c>
-      <c r="F4" t="str">
-        <v>/api/v1/products</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #19</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>VULN_004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Business Logic Security</v>
-      </c>
-      <c r="D5" t="str">
-        <v>CWE-222</v>
-      </c>
-      <c r="E5" t="str">
-        <v>A02:2021</v>
-      </c>
-      <c r="F5" t="str">
-        <v>/api/v1/orders</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #2</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>VULN_005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MEDIUM</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Security Configurations &amp; CORS</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CWE-215</v>
-      </c>
-      <c r="E6" t="str">
-        <v>A09:2021</v>
-      </c>
-      <c r="F6" t="str">
-        <v>/api/v1/orders</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #15</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>VULN_006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>HIGH</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Functional API Security</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CWE-208</v>
-      </c>
-      <c r="E7" t="str">
-        <v>A07:2021</v>
-      </c>
-      <c r="F7" t="str">
-        <v>/api/v1/ai/match-items</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #28</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>VULN_007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Functional API Security</v>
-      </c>
-      <c r="D8" t="str">
-        <v>CWE-201</v>
-      </c>
-      <c r="E8" t="str">
-        <v>A05:2021</v>
-      </c>
-      <c r="F8" t="str">
-        <v>/api/v1/auth/login</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #71</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>VULN_008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Performance &amp; Throttling Security</v>
-      </c>
-      <c r="D9" t="str">
-        <v>CWE-244</v>
-      </c>
-      <c r="E9" t="str">
-        <v>A03:2021</v>
-      </c>
-      <c r="F9" t="str">
-        <v>/api/v1/auth/register</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #14</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>VULN_009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>MEDIUM</v>
-      </c>
-      <c r="C10" t="str">
-        <v>DAST Vulnerability Scans</v>
-      </c>
-      <c r="D10" t="str">
-        <v>CWE-237</v>
-      </c>
-      <c r="E10" t="str">
-        <v>A01:2021</v>
-      </c>
-      <c r="F10" t="str">
-        <v>/api/v1/products</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Potential security weakness detected during automated SAST/DAST scanning pattern #27</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Possible unauthorized data disclosure or improper input processing under stress</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Enforce parameterized queries, strict schema validation, and security headers</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>